--- a/output/4988/1.xlsx
+++ b/output/4988/1.xlsx
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C1:J31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col hidden="1" width="0.727272727272727" customWidth="1" style="1" min="1" max="1"/>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
+      <c r="G5" s="5" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr">
         <is>
           <t>2</t>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
+      <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr">
         <is>
           <t>1</t>
@@ -1165,16 +1165,16 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>17000240</t>
+          <t>17000051</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>SLIN-静电计支撑块-ODBC</t>
+          <t>ODBC定制线</t>
         </is>
       </c>
       <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
+      <c r="G7" s="6" t="inlineStr"/>
       <c r="H7" s="6" t="inlineStr">
         <is>
           <t>1</t>
@@ -1188,37 +1188,79 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>17000051</t>
+          <t>17000240</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>ODBC定制线</t>
+          <t>STRU-风扇密封-ODBC：DRW-Part-ODBC-0024</t>
         </is>
       </c>
       <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="C9" s="5" t="n"/>
-      <c r="E9" s="2" t="n"/>
+      <c r="C9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>17000060</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>STRU-Cart垃圾桶-ODBC：DRW-Part-ODBC-0006</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="I9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="C10" s="5" t="n"/>
-      <c r="E10" s="2" t="n"/>
+      <c r="C10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>17000050</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>STRU-Tip&amp;Slide垃圾桶-ODBC：DRW-Part-ODBC-0005</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="n"/>
     </row>
     <row r="11">
